--- a/tables/Stage.xlsx
+++ b/tables/Stage.xlsx
@@ -479,7 +479,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>스테이지 순서·BGM·스폰 파일.</t>
+          <t>CSV,스테이지 순서·BGM·스폰 파일.</t>
         </is>
       </c>
       <c r="C2" s="1" t="n"/>

--- a/tables/Stage.xlsx
+++ b/tables/Stage.xlsx
@@ -435,351 +435,359 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10.13" customWidth="1" min="1" max="1"/>
-    <col width="7.88" customWidth="1" min="2" max="2"/>
-    <col width="5" customWidth="1" min="3" max="3"/>
-    <col width="8.630000000000001" customWidth="1" min="4" max="4"/>
-    <col width="11.5" customWidth="1" min="5" max="5"/>
-    <col width="10.88" customWidth="1" min="6" max="6"/>
-    <col width="14.38" customWidth="1" min="7" max="7"/>
-    <col width="22.25" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>규칙</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>한 행 = 스테이지 하나. NextStage는 다음 Stage ID(비면 마지막). 스폰 JSON의 code는 Monster ID. 13행부터의 JSON 예시는 내보내지 않음.</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>기능</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>CSV,스테이지 순서·BGM·스폰 파일.</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="n"/>
-      <c r="D2" s="1" t="n"/>
-      <c r="E2" s="1" t="n"/>
-      <c r="F2" s="1" t="n"/>
-      <c r="G2" s="1" t="n"/>
-      <c r="H2" s="1" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>역할</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>스테이지 로더가 읽는다. StageLayer가 이 ID로 매달림.</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="n"/>
-      <c r="D3" s="1" t="n"/>
-      <c r="E3" s="1" t="n"/>
-      <c r="F3" s="1" t="n"/>
-      <c r="G3" s="1" t="n"/>
-      <c r="H3" s="1" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>의도</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>맵 순서와 배치를 코드 수정 없이 바꾸기 위해.</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="n"/>
-      <c r="D4" s="1" t="n"/>
-      <c r="E4" s="1" t="n"/>
-      <c r="F4" s="1" t="n"/>
-      <c r="G4" s="1" t="n"/>
-      <c r="H4" s="1" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>Name, Note</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="n"/>
-      <c r="D5" s="1" t="n"/>
-      <c r="E5" s="1" t="n"/>
-      <c r="F5" s="1" t="n"/>
-      <c r="G5" s="1" t="n"/>
-      <c r="H5" s="1" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>TextID</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Order</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>NextStage</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>BGM_Normal</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>BGM_Battle</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>SpawnFile</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>8001</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>마을(도화골)</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>30011</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>8002</v>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>BGM_VILLAGE</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>BGM_BATTLE</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>spawn/8001.json</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>인트로 컷씬 뒤, 부상당한 피난민 NPC</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="n">
-        <v>8002</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>사냥터 1</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>30012</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>8003</v>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>BGM_FIELD</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>BGM_BATTLE</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>spawn/8002.json</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n">
-        <v>8003</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>사냥터 2</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>30013</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>8004</v>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>BGM_FIELD</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>BGM_BATTLE</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>spawn/8003.json</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>장부방(결박 가르기 해금)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>8004</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>보스방</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>30014</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>BGM_BOSS</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>spawn/8004.json</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>전투 BGM BPM 낮춤 버전(10/28)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>스폰 JSON 예시 (10/28 회의: 몬스터 코드 + count, 위치도 JSON, 초기엔 확률 없음. code = Monster ID)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>{"stage":8002,"spawns":[{"code":3001,"count":3,"points":[[1200,0],[1800,0],[2600,0]]},{"code":3002,"count":1,"points":[[3400,0]]}]}</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>맵당 몬스터 2종 + 보스 1(지스타 범위). 배치는 제안이며 레벨 디자인에서 확정</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
+<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <ns0:sheetPr>
+    <ns0:outlinePr summaryBelow="1" summaryRight="1"/>
+    <ns0:pageSetUpPr/>
+  </ns0:sheetPr>
+  <ns0:dimension ref="A1:J15"/>
+  <ns0:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <ns0:cols>
+    <ns0:col width="10.13" customWidth="1" min="1" max="1"/>
+    <ns0:col width="7.88" customWidth="1" min="2" max="2"/>
+    <ns0:col width="5" customWidth="1" min="3" max="3"/>
+    <ns0:col width="8.630000000000001" customWidth="1" min="4" max="4"/>
+    <ns0:col width="11.5" customWidth="1" min="5" max="5"/>
+    <ns0:col width="10.88" customWidth="1" min="6" max="6"/>
+    <ns0:col width="14.38" customWidth="1" min="7" max="7"/>
+    <ns0:col width="22.25" customWidth="1" min="8" max="8"/>
+  </ns0:cols>
+  <ns0:sheetData>
+    <ns0:row r="1">
+      <ns0:c r="A1" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>규칙</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B1" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t xml:space="preserve">한 행 = 스테이지 하나. NextStage는 다음 Stage ID(비면 마지막). 스폰 JSON의 code는 Monster ID. 13행부터의 JSON 예시는 내보내지 않음.
+[추출 지정 규칙]
+@column Name=TextID;Type=Integer;Minimum=1;ReferenceTable=Language
+@column Name=Order;Type=Integer;Minimum=1
+@column Name=NextStage;Type=Integer;Optional=Y;Minimum=1;ReferenceTable=Stage
+@column Name=BGM_Normal;Type=Text;Optional=Y
+@column Name=BGM_Battle;Type=Text;Optional=Y
+@column Name=SpawnFile;Type=Text
+@column Name=Active;Type=Flag</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C1" s="1" t="n"/>
+      <ns0:c r="D1" s="1" t="n"/>
+      <ns0:c r="E1" s="1" t="n"/>
+      <ns0:c r="F1" s="1" t="n"/>
+      <ns0:c r="G1" s="1" t="n"/>
+      <ns0:c r="H1" s="1" t="n"/>
+    </ns0:row>
+    <ns0:row r="2">
+      <ns0:c r="A2" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>기능</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B2" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>CSV,스테이지 순서·BGM·스폰 파일.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C2" s="1" t="n"/>
+      <ns0:c r="D2" s="1" t="n"/>
+      <ns0:c r="E2" s="1" t="n"/>
+      <ns0:c r="F2" s="1" t="n"/>
+      <ns0:c r="G2" s="1" t="n"/>
+      <ns0:c r="H2" s="1" t="n"/>
+    </ns0:row>
+    <ns0:row r="3">
+      <ns0:c r="A3" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>역할</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B3" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>스테이지 로더가 읽는다. StageLayer가 이 ID로 매달림.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C3" s="1" t="n"/>
+      <ns0:c r="D3" s="1" t="n"/>
+      <ns0:c r="E3" s="1" t="n"/>
+      <ns0:c r="F3" s="1" t="n"/>
+      <ns0:c r="G3" s="1" t="n"/>
+      <ns0:c r="H3" s="1" t="n"/>
+    </ns0:row>
+    <ns0:row r="4">
+      <ns0:c r="A4" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>의도</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B4" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>맵 순서와 배치를 코드 수정 없이 바꾸기 위해.</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C4" s="1" t="n"/>
+      <ns0:c r="D4" s="1" t="n"/>
+      <ns0:c r="E4" s="1" t="n"/>
+      <ns0:c r="F4" s="1" t="n"/>
+      <ns0:c r="G4" s="1" t="n"/>
+      <ns0:c r="H4" s="1" t="n"/>
+    </ns0:row>
+    <ns0:row r="5">
+      <ns0:c r="A5" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>비고</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B5" s="1" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Name, Note</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C5" s="1" t="n"/>
+      <ns0:c r="D5" s="1" t="n"/>
+      <ns0:c r="E5" s="1" t="n"/>
+      <ns0:c r="F5" s="1" t="n"/>
+      <ns0:c r="G5" s="1" t="n"/>
+      <ns0:c r="H5" s="1" t="n"/>
+    </ns0:row>
+    <ns0:row r="6">
+      <ns0:c r="A6" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>ID</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="B6" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Name</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C6" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>TextID</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="D6" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Order</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="E6" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>NextStage</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="F6" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>BGM_Normal</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G6" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>BGM_Battle</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H6" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>SpawnFile</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I6" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Active</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J6" s="2" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Note</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="7">
+      <ns0:c r="A7" s="3" t="n">
+        <ns0:v>8001</ns0:v>
+      </ns0:c>
+      <ns0:c r="B7" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>마을(도화골)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C7" s="3" t="n">
+        <ns0:v>30011</ns0:v>
+      </ns0:c>
+      <ns0:c r="D7" s="3" t="n">
+        <ns0:v>1</ns0:v>
+      </ns0:c>
+      <ns0:c r="E7" s="3" t="n">
+        <ns0:v>8002</ns0:v>
+      </ns0:c>
+      <ns0:c r="F7" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>BGM_VILLAGE</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G7" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>BGM_BATTLE</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H7" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>spawn/8001.json</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I7" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Y</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J7" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>인트로 컷씬 뒤, 부상당한 피난민 NPC</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="8">
+      <ns0:c r="A8" s="3" t="n">
+        <ns0:v>8002</ns0:v>
+      </ns0:c>
+      <ns0:c r="B8" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>사냥터 1</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C8" s="3" t="n">
+        <ns0:v>30012</ns0:v>
+      </ns0:c>
+      <ns0:c r="D8" s="3" t="n">
+        <ns0:v>2</ns0:v>
+      </ns0:c>
+      <ns0:c r="E8" s="3" t="n">
+        <ns0:v>8003</ns0:v>
+      </ns0:c>
+      <ns0:c r="F8" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>BGM_FIELD</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G8" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>BGM_BATTLE</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H8" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>spawn/8002.json</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I8" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Y</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="9">
+      <ns0:c r="A9" s="3" t="n">
+        <ns0:v>8003</ns0:v>
+      </ns0:c>
+      <ns0:c r="B9" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>사냥터 2</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C9" s="3" t="n">
+        <ns0:v>30013</ns0:v>
+      </ns0:c>
+      <ns0:c r="D9" s="3" t="n">
+        <ns0:v>3</ns0:v>
+      </ns0:c>
+      <ns0:c r="E9" s="3" t="n">
+        <ns0:v>8004</ns0:v>
+      </ns0:c>
+      <ns0:c r="F9" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>BGM_FIELD</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="G9" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>BGM_BATTLE</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H9" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>spawn/8003.json</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I9" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Y</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J9" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>장부방(결박 가르기 해금)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="10">
+      <ns0:c r="A10" s="3" t="n">
+        <ns0:v>8004</ns0:v>
+      </ns0:c>
+      <ns0:c r="B10" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>보스방</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="C10" s="3" t="n">
+        <ns0:v>30014</ns0:v>
+      </ns0:c>
+      <ns0:c r="D10" s="3" t="n">
+        <ns0:v>4</ns0:v>
+      </ns0:c>
+      <ns0:c r="G10" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>BGM_BOSS</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="H10" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>spawn/8004.json</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="I10" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>Y</ns0:t>
+        </ns0:is>
+      </ns0:c>
+      <ns0:c r="J10" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>전투 BGM BPM 낮춤 버전(10/28)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="13">
+      <ns0:c r="A13" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>스폰 JSON 예시 (10/28 회의: 몬스터 코드 + count, 위치도 JSON, 초기엔 확률 없음. code = Monster ID)</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="14">
+      <ns0:c r="A14" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>{"stage":8002,"spawns":[{"code":3001,"count":3,"points":[[1200,0],[1800,0],[2600,0]]},{"code":3002,"count":1,"points":[[3400,0]]}]}</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+    <ns0:row r="15">
+      <ns0:c r="A15" s="3" t="inlineStr">
+        <ns0:is>
+          <ns0:t>맵당 몬스터 2종 + 보스 1(지스타 범위). 배치는 제안이며 레벨 디자인에서 확정</ns0:t>
+        </ns0:is>
+      </ns0:c>
+    </ns0:row>
+  </ns0:sheetData>
+  <ns0:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</ns0:worksheet>
 </file>
--- a/tables/Stage.xlsx
+++ b/tables/Stage.xlsx
@@ -435,33 +435,33 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<ns0:worksheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <ns0:sheetPr>
-    <ns0:outlinePr summaryBelow="1" summaryRight="1"/>
-    <ns0:pageSetUpPr/>
-  </ns0:sheetPr>
-  <ns0:dimension ref="A1:J15"/>
-  <ns0:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <ns0:cols>
-    <ns0:col width="10.13" customWidth="1" min="1" max="1"/>
-    <ns0:col width="7.88" customWidth="1" min="2" max="2"/>
-    <ns0:col width="5" customWidth="1" min="3" max="3"/>
-    <ns0:col width="8.630000000000001" customWidth="1" min="4" max="4"/>
-    <ns0:col width="11.5" customWidth="1" min="5" max="5"/>
-    <ns0:col width="10.88" customWidth="1" min="6" max="6"/>
-    <ns0:col width="14.38" customWidth="1" min="7" max="7"/>
-    <ns0:col width="22.25" customWidth="1" min="8" max="8"/>
-  </ns0:cols>
-  <ns0:sheetData>
-    <ns0:row r="1">
-      <ns0:c r="A1" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>규칙</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B1" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t xml:space="preserve">한 행 = 스테이지 하나. NextStage는 다음 Stage ID(비면 마지막). 스폰 JSON의 code는 Monster ID. 13행부터의 JSON 예시는 내보내지 않음.
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10.13" customWidth="1" min="1" max="1"/>
+    <col width="7.88" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="3" max="3"/>
+    <col width="8.630000000000001" customWidth="1" min="4" max="4"/>
+    <col width="11.5" customWidth="1" min="5" max="5"/>
+    <col width="10.88" customWidth="1" min="6" max="6"/>
+    <col width="14.38" customWidth="1" min="7" max="7"/>
+    <col width="22.25" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>규칙</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>한 행 = 스테이지 하나. NextStage는 다음 Stage ID(비면 마지막). 스폰 JSON의 code는 Monster ID. 13행부터의 JSON 예시는 내보내지 않음.
 [추출 지정 규칙]
 @column Name=TextID;Type=Integer;Minimum=1;ReferenceTable=Language
 @column Name=Order;Type=Integer;Minimum=1
@@ -469,325 +469,331 @@
 @column Name=BGM_Normal;Type=Text;Optional=Y
 @column Name=BGM_Battle;Type=Text;Optional=Y
 @column Name=SpawnFile;Type=Text
-@column Name=Active;Type=Flag</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C1" s="1" t="n"/>
-      <ns0:c r="D1" s="1" t="n"/>
-      <ns0:c r="E1" s="1" t="n"/>
-      <ns0:c r="F1" s="1" t="n"/>
-      <ns0:c r="G1" s="1" t="n"/>
-      <ns0:c r="H1" s="1" t="n"/>
-    </ns0:row>
-    <ns0:row r="2">
-      <ns0:c r="A2" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>기능</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B2" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>CSV,스테이지 순서·BGM·스폰 파일.</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C2" s="1" t="n"/>
-      <ns0:c r="D2" s="1" t="n"/>
-      <ns0:c r="E2" s="1" t="n"/>
-      <ns0:c r="F2" s="1" t="n"/>
-      <ns0:c r="G2" s="1" t="n"/>
-      <ns0:c r="H2" s="1" t="n"/>
-    </ns0:row>
-    <ns0:row r="3">
-      <ns0:c r="A3" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>역할</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B3" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>스테이지 로더가 읽는다. StageLayer가 이 ID로 매달림.</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C3" s="1" t="n"/>
-      <ns0:c r="D3" s="1" t="n"/>
-      <ns0:c r="E3" s="1" t="n"/>
-      <ns0:c r="F3" s="1" t="n"/>
-      <ns0:c r="G3" s="1" t="n"/>
-      <ns0:c r="H3" s="1" t="n"/>
-    </ns0:row>
-    <ns0:row r="4">
-      <ns0:c r="A4" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>의도</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B4" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>맵 순서와 배치를 코드 수정 없이 바꾸기 위해.</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C4" s="1" t="n"/>
-      <ns0:c r="D4" s="1" t="n"/>
-      <ns0:c r="E4" s="1" t="n"/>
-      <ns0:c r="F4" s="1" t="n"/>
-      <ns0:c r="G4" s="1" t="n"/>
-      <ns0:c r="H4" s="1" t="n"/>
-    </ns0:row>
-    <ns0:row r="5">
-      <ns0:c r="A5" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>비고</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B5" s="1" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Name, Note</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C5" s="1" t="n"/>
-      <ns0:c r="D5" s="1" t="n"/>
-      <ns0:c r="E5" s="1" t="n"/>
-      <ns0:c r="F5" s="1" t="n"/>
-      <ns0:c r="G5" s="1" t="n"/>
-      <ns0:c r="H5" s="1" t="n"/>
-    </ns0:row>
-    <ns0:row r="6">
-      <ns0:c r="A6" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>ID</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="B6" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Name</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C6" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>TextID</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="D6" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Order</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="E6" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>NextStage</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="F6" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>BGM_Normal</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="G6" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>BGM_Battle</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="H6" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>SpawnFile</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I6" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Active</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="J6" s="2" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Note</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="7">
-      <ns0:c r="A7" s="3" t="n">
-        <ns0:v>8001</ns0:v>
-      </ns0:c>
-      <ns0:c r="B7" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>마을(도화골)</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C7" s="3" t="n">
-        <ns0:v>30011</ns0:v>
-      </ns0:c>
-      <ns0:c r="D7" s="3" t="n">
-        <ns0:v>1</ns0:v>
-      </ns0:c>
-      <ns0:c r="E7" s="3" t="n">
-        <ns0:v>8002</ns0:v>
-      </ns0:c>
-      <ns0:c r="F7" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>BGM_VILLAGE</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="G7" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>BGM_BATTLE</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="H7" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>spawn/8001.json</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I7" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Y</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="J7" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>인트로 컷씬 뒤, 부상당한 피난민 NPC</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="8">
-      <ns0:c r="A8" s="3" t="n">
-        <ns0:v>8002</ns0:v>
-      </ns0:c>
-      <ns0:c r="B8" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>사냥터 1</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C8" s="3" t="n">
-        <ns0:v>30012</ns0:v>
-      </ns0:c>
-      <ns0:c r="D8" s="3" t="n">
-        <ns0:v>2</ns0:v>
-      </ns0:c>
-      <ns0:c r="E8" s="3" t="n">
-        <ns0:v>8003</ns0:v>
-      </ns0:c>
-      <ns0:c r="F8" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>BGM_FIELD</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="G8" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>BGM_BATTLE</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="H8" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>spawn/8002.json</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I8" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Y</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="9">
-      <ns0:c r="A9" s="3" t="n">
-        <ns0:v>8003</ns0:v>
-      </ns0:c>
-      <ns0:c r="B9" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>사냥터 2</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C9" s="3" t="n">
-        <ns0:v>30013</ns0:v>
-      </ns0:c>
-      <ns0:c r="D9" s="3" t="n">
-        <ns0:v>3</ns0:v>
-      </ns0:c>
-      <ns0:c r="E9" s="3" t="n">
-        <ns0:v>8004</ns0:v>
-      </ns0:c>
-      <ns0:c r="F9" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>BGM_FIELD</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="G9" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>BGM_BATTLE</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="H9" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>spawn/8003.json</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I9" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Y</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="J9" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>장부방(결박 가르기 해금)</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="10">
-      <ns0:c r="A10" s="3" t="n">
-        <ns0:v>8004</ns0:v>
-      </ns0:c>
-      <ns0:c r="B10" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>보스방</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="C10" s="3" t="n">
-        <ns0:v>30014</ns0:v>
-      </ns0:c>
-      <ns0:c r="D10" s="3" t="n">
-        <ns0:v>4</ns0:v>
-      </ns0:c>
-      <ns0:c r="G10" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>BGM_BOSS</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="H10" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>spawn/8004.json</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="I10" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>Y</ns0:t>
-        </ns0:is>
-      </ns0:c>
-      <ns0:c r="J10" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>전투 BGM BPM 낮춤 버전(10/28)</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="13">
-      <ns0:c r="A13" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>스폰 JSON 예시 (10/28 회의: 몬스터 코드 + count, 위치도 JSON, 초기엔 확률 없음. code = Monster ID)</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="14">
-      <ns0:c r="A14" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>{"stage":8002,"spawns":[{"code":3001,"count":3,"points":[[1200,0],[1800,0],[2600,0]]},{"code":3002,"count":1,"points":[[3400,0]]}]}</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-    <ns0:row r="15">
-      <ns0:c r="A15" s="3" t="inlineStr">
-        <ns0:is>
-          <ns0:t>맵당 몬스터 2종 + 보스 1(지스타 범위). 배치는 제안이며 레벨 디자인에서 확정</ns0:t>
-        </ns0:is>
-      </ns0:c>
-    </ns0:row>
-  </ns0:sheetData>
-  <ns0:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</ns0:worksheet>
+@column Name=Active;Type=Flag</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>기능</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>CSV,스테이지 순서·BGM·스폰 파일.</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>역할</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>스테이지 로더가 읽는다. StageLayer가 이 ID로 매달림.</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="n"/>
+      <c r="D3" s="1" t="n"/>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
+      <c r="H3" s="1" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>의도</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>맵 순서와 배치를 코드 수정 없이 바꾸기 위해.</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="n"/>
+      <c r="D4" s="1" t="n"/>
+      <c r="E4" s="1" t="n"/>
+      <c r="F4" s="1" t="n"/>
+      <c r="G4" s="1" t="n"/>
+      <c r="H4" s="1" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>Name, Note</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="n"/>
+      <c r="D5" s="1" t="n"/>
+      <c r="E5" s="1" t="n"/>
+      <c r="F5" s="1" t="n"/>
+      <c r="G5" s="1" t="n"/>
+      <c r="H5" s="1" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>TextID</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Order</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>NextStage</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>BGM_Normal</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>BGM_Battle</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>SpawnFile</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>8001</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>마을(도화골)</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>30011</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>8002</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>BGM_VILLAGE</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>BGM_BATTLE</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>spawn/8001.json</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>인트로 컷씬 뒤, 부상당한 피난민 NPC</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>8002</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>산길 초입구</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>30012</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>8003</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>BGM_FIELD</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>BGM_BATTLE</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>spawn/8002.json</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>8003</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>산길 위 바위 협곡</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>30013</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>8004</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>BGM_FIELD</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>BGM_BATTLE</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>spawn/8003.json</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>장부방(결박 가르기 해금)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>8004</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>관문(보스방)</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>30014</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>BGM_BOSS</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>spawn/8004.json</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>전투 BGM BPM 낮춤 버전(10/28)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>스폰 JSON 예시 (10/28 회의: 몬스터 코드 + count, 위치도 JSON, 초기엔 확률 없음. code = Monster ID)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>{"stage":8002,"spawns":[{"code":3001,"count":3,"points":[[1200,0],[1800,0],[2600,0]]},{"code":3002,"count":1,"points":[[3400,0]]}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>맵당 몬스터 2종 + 보스 1(지스타 범위). 배치는 제안이며 레벨 디자인에서 확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/tables/Stage.xlsx
+++ b/tables/Stage.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.13" customWidth="1" min="1" max="1"/>
@@ -643,7 +643,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>인트로 컷씬 뒤, 부상당한 피난민 NPC</t>
+          <t>인트로 컷씬 뒤, 부상당한 피난민 NPC. 마을 안 장부방(결박 가르기 해금, 맵 2 전)</t>
         </is>
       </c>
     </row>
@@ -724,11 +724,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>장부방(결박 가르기 해금)</t>
-        </is>
-      </c>
+      <c r="J9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -766,8 +762,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
@@ -789,10 +783,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tables/Stage.xlsx
+++ b/tables/Stage.xlsx
@@ -619,7 +619,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>8002</v>
+        <v>8005</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>인트로 컷씬 뒤, 부상당한 피난민 NPC. 마을 안 장부방(결박 가르기 해금, 맵 2 전)</t>
+          <t>인트로 컷씬 뒤, 부상당한 피난민 NPC. 다음은 장부방(8005)</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
         <v>30012</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>8003</v>
@@ -699,7 +699,7 @@
         <v>30013</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>8004</v>
@@ -739,7 +739,7 @@
         <v>30014</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
@@ -759,6 +759,42 @@
       <c r="J10" s="3" t="inlineStr">
         <is>
           <t>전투 BGM BPM 낮춤 버전(10/28)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>8005</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>장부방</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>30027</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>8002</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>BGM_VILLAGE</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>마을 안 작은 실내 맵. 몬스터 없음(스폰 파일 없음). 명부 조사(E) → 일러스트 연출로 결박 가르기 해금(10/30 확정)</t>
         </is>
       </c>
     </row>
